--- a/programs/access-476a07b27d/VOLTR-Hybrid.xlsx
+++ b/programs/access-476a07b27d/VOLTR-Hybrid.xlsx
@@ -669,7 +669,6 @@
           <t>VOLTR · HYBRID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
@@ -679,7 +678,6 @@
           <t>8 weeks  ·  3 strength sessions + 3 runs per week  ·  full gym</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n"/>
       <c r="D2" s="3" t="n"/>
     </row>
     <row r="3" ht="10" customHeight="1"/>
@@ -777,7 +775,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Zone 2 (Z2), easy: RPE 3 to 4, full sentences, nose breathing most of the time. With a heart rate monitor, roughly 70 to 80 percent of max heart rate.
+          <t>Zone 2 (Z2), easy: RPE 3 to 4, full sentences, nose breathing most of the time. With a heart rate monitor, roughly 65 to 75 percent of max heart rate.
 Tempo: RPE 6 to 7, comfortably hard.
 Intervals: RPE 8, hard and even. The last rep as fast as the first.
 Strides: 20 s fast and relaxed, then walk back.
@@ -934,22 +932,11 @@
           <t>INFO</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n"/>
       <c r="C2" s="14" t="inlineStr">
         <is>
           <t>Block 1 sets the baseline in week 1 (3 km time trial) and builds strength and running volume together. Lifting stays at RIR 2 to 3 so the runs keep their quality. Running time rises about 10 percent per week. Week 4 is a deload for both: fewer sets, shorter runs, no hard intervals. Suggested week: Mon A, Tue Run 1, Wed B, Thu Run 2, Fri C, Sat off, Sun Run 3.</t>
         </is>
       </c>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="14" t="n"/>
-      <c r="F2" s="14" t="n"/>
-      <c r="G2" s="14" t="n"/>
-      <c r="H2" s="14" t="n"/>
-      <c r="I2" s="14" t="n"/>
-      <c r="J2" s="14" t="n"/>
-      <c r="K2" s="14" t="n"/>
-      <c r="L2" s="14" t="n"/>
-      <c r="M2" s="14" t="n"/>
     </row>
     <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="22" customHeight="1">
@@ -2151,13 +2138,13 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="L4:M4"/>
-    <mergeCell ref="C30:E30"/>
     <mergeCell ref="C1:M1"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="C2:M2"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H4:I4"/>
+    <mergeCell ref="C30:E30"/>
     <mergeCell ref="C7:E7"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -2208,22 +2195,11 @@
           <t>INFO</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n"/>
       <c r="C2" s="14" t="inlineStr">
         <is>
           <t>Block 2 lowers the reps on the main lifts, adds load, and moves the quality run from short intervals to longer efforts. Running time keeps rising until week 7. Week 8 is the test: top sets Monday and Wednesday, 3 km time trial Thursday, reduced volume around them. Compare every benchmark with week 1 on the LOG tab.</t>
         </is>
       </c>
-      <c r="D2" s="14" t="n"/>
-      <c r="E2" s="14" t="n"/>
-      <c r="F2" s="14" t="n"/>
-      <c r="G2" s="14" t="n"/>
-      <c r="H2" s="14" t="n"/>
-      <c r="I2" s="14" t="n"/>
-      <c r="J2" s="14" t="n"/>
-      <c r="K2" s="14" t="n"/>
-      <c r="L2" s="14" t="n"/>
-      <c r="M2" s="14" t="n"/>
     </row>
     <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="22" customHeight="1">
@@ -3421,13 +3397,13 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="L4:M4"/>
-    <mergeCell ref="C30:E30"/>
     <mergeCell ref="C1:M1"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="C2:M2"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H4:I4"/>
+    <mergeCell ref="C30:E30"/>
     <mergeCell ref="C7:E7"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3470,12 +3446,6 @@
           <t>Fill in once a week, same day, same time. Benchmarks in week 1 and week 8.</t>
         </is>
       </c>
-      <c r="C2" s="30" t="n"/>
-      <c r="D2" s="30" t="n"/>
-      <c r="E2" s="30" t="n"/>
-      <c r="F2" s="30" t="n"/>
-      <c r="G2" s="30" t="n"/>
-      <c r="H2" s="30" t="n"/>
     </row>
     <row r="3"/>
     <row r="4" ht="22" customHeight="1">

--- a/programs/access-476a07b27d/VOLTR-Hybrid.xlsx
+++ b/programs/access-476a07b27d/VOLTR-Hybrid.xlsx
@@ -726,7 +726,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Eight weeks, three strength sessions of 50 to 65 minutes and three runs per week. Running volume rises steadily, and heavy leg work sits at least 48 hours before the quality run. Week 1 and week 8 both include a 3 km time trial and top sets on the main lifts, so you see whether you got stronger and faster together.</t>
+          <t>Eight weeks, three strength sessions of 50 to 65 minutes and three runs per week. Running volume rises steadily, and heavy leg work sits at least 48 hours before the quality run. Week 1 and week 8 both include a 3 km time trial and top sets on squat and bench, so you see whether you got stronger and faster together.</t>
         </is>
       </c>
     </row>
@@ -843,8 +843,8 @@
       <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Main lifts: add 2.5 kg (lower body) or 1 to 2.5 kg (bench) each week as long as last week's sets matched the target RIR. Accessories: double progression, add the smallest step once all sets reach the top of the rep range. RIR stays at 2 to 3 on most sets so the quality run stays quality.
-Running: total time rises in weeks 1 to 3 and 5 to 7. The long run never gets more than about 10 percent longer than your longest run of the previous month, because single long jumps are what drive running injuries.
-Week 4: deload for both. Week 8: test week, top sets Monday and Wednesday, 3 km time trial Thursday.</t>
+Running: total time rises in weeks 1 to 3 and 5 to 7. The long run grows by about four minutes a week, with a shorter week 4, because sudden jumps in running volume are a common cause of overuse problems.
+Week 4: deload for both. Week 1 and week 8: top sets Monday and Wednesday, 3 km time trial Thursday, heart rate test on the Tuesday run.</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Missed a strength session: do the next one in order, never two on one day.
-Missed the quality run: do it at the next run slot if that is at least 48 hours after Strength A, otherwise skip it this week. Never the day before the long run.
+Missed the quality run: skip it this week. Never turn the long run into a quality session.
 Missed a full week: repeat the last complete week.
 Bad day: sets, reps and run efforts stay as written, load and pace follow the effort. Log it.
 Legs heavy for more than a week, sleep worse, resting heart rate up: run the week 4 structure once, then continue.</t>
@@ -901,7 +901,7 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>1:1 coaching builds the program around your schedule, travel and training history. Book a 30-minute call: https://calendly.com/training-voltr/30min</t>
+          <t>1:1 coaching builds the program around your schedule, travel and training history. Book a 30-minute call: https://voltr.at/#book</t>
         </is>
       </c>
       <c r="D17" s="7" t="n"/>
@@ -972,7 +972,7 @@
       </c>
       <c r="C2" s="14" t="inlineStr">
         <is>
-          <t>Block 1 sets the baseline in week 1 (3 km time trial) and builds strength and running volume together. Lifting stays at RIR 2 to 3 so the runs keep their quality. Running time rises about 10 percent per week. Week 4 is a deload for both: fewer sets, shorter runs, no hard intervals. Suggested week: Mon A, Tue Run 1, Wed B, Thu Run 2, Fri C, Sat off, Sun Run 3.</t>
+          <t>Block 1 sets the baseline in week 1 (3 km time trial) and builds strength and running volume together. Lifting stays at RIR 2 to 3 so the runs keep their quality. Running time rises gradually from week to week. Week 4 is a deload for both: fewer sets, shorter runs, no hard intervals. Suggested week: Mon A, Tue Run 1, Wed B, Thu Run 2, Fri C, Sat off, Sun Run 3.</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>Monday. At least 48 hours before the quality run. About 60 minutes.</t>
+          <t>Monday. At least 48 hours before the quality run. About 60 minutes. Week 1: benchmark top set on the squat.</t>
         </is>
       </c>
       <c r="F7" s="7" t="n"/>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>3 x 5 @ RIR 3</t>
+          <t>Top set 1 x 5 @ RIR 2 (benchmark), then 2 x 5 @ RIR 3</t>
         </is>
       </c>
       <c r="G8" s="26" t="n"/>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>3 x 5-8 @ RIR 3</t>
+          <t>Set 1: max strict reps (benchmark), then 2 x 5-8 @ RIR 3</t>
         </is>
       </c>
       <c r="G10" s="26" t="n"/>
@@ -1302,45 +1302,45 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>Pallof press</t>
+          <t>Nordic hamstring curl</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>Cable at chest height, side-on. Press out, hold 3 s, return. The torso does not turn.</t>
+          <t>Heels anchored. Lower forward as slowly as you can, catch with the hands, push back up. Use a band for help if needed.</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>3 s hold</t>
+          <t>slow lower</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>45 s</t>
+          <t>90 s</t>
         </is>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>2 x 10/side</t>
+          <t>2 x 4</t>
         </is>
       </c>
       <c r="G12" s="26" t="n"/>
       <c r="H12" s="27" t="inlineStr">
         <is>
-          <t>3 x 10/side</t>
+          <t>2 x 5</t>
         </is>
       </c>
       <c r="I12" s="28" t="n"/>
       <c r="J12" s="25" t="inlineStr">
         <is>
-          <t>3 x 10/side</t>
+          <t>3 x 5</t>
         </is>
       </c>
       <c r="K12" s="26" t="n"/>
       <c r="L12" s="27" t="inlineStr">
         <is>
-          <t>2 x 10/side</t>
+          <t>1 x 4</t>
         </is>
       </c>
       <c r="M12" s="28" t="n"/>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>4 x 6 @ RIR 3</t>
+          <t>Top set 1 x 5 @ RIR 2 (benchmark), then 3 x 6 @ RIR 3</t>
         </is>
       </c>
       <c r="G15" s="26" t="n"/>
@@ -1856,45 +1856,45 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>Nordic hamstring curl</t>
+          <t>Pallof press</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>Heels anchored. Lower forward as slowly as you can, catch with the hands, push back up. Use a band for help if needed.</t>
+          <t>Cable at chest height, side-on. Press out, hold 3 s, return. The torso does not turn.</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>slow lower</t>
+          <t>3 s hold</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
         <is>
-          <t>90 s</t>
+          <t>45 s</t>
         </is>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>2 x 4</t>
+          <t>2 x 10/side</t>
         </is>
       </c>
       <c r="G26" s="26" t="n"/>
       <c r="H26" s="27" t="inlineStr">
         <is>
-          <t>2 x 5</t>
+          <t>3 x 10/side</t>
         </is>
       </c>
       <c r="I26" s="28" t="n"/>
       <c r="J26" s="25" t="inlineStr">
         <is>
-          <t>3 x 5</t>
+          <t>3 x 10/side</t>
         </is>
       </c>
       <c r="K26" s="26" t="n"/>
       <c r="L26" s="27" t="inlineStr">
         <is>
-          <t>1 x 4</t>
+          <t>2 x 10/side</t>
         </is>
       </c>
       <c r="M26" s="28" t="n"/>
@@ -2043,7 +2043,7 @@
       <c r="E31" s="24" t="n"/>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>30 min Z2</t>
+          <t>30 min Z2: first 20 min at your fixed test pace (heart rate benchmark)</t>
         </is>
       </c>
       <c r="G31" s="26" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="K10" s="26" t="n"/>
       <c r="L10" s="27" t="inlineStr">
         <is>
-          <t>2 x 4 @ RIR 3</t>
+          <t>Set 1: max strict reps at bodyweight (benchmark), then 1 x 4 @ RIR 3</t>
         </is>
       </c>
       <c r="M10" s="28" t="n"/>
@@ -2565,45 +2565,45 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>Half-kneeling cable lift</t>
+          <t>Nordic hamstring curl</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>Cable low on the side of the down knee. Pull up and across, hips stay square.</t>
+          <t>Slower lowering than in block 1. Less band help if you used one.</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>controlled</t>
+          <t>slow lower</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>45 s</t>
+          <t>90 s</t>
         </is>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>3 x 8/side</t>
+          <t>3 x 5</t>
         </is>
       </c>
       <c r="G12" s="26" t="n"/>
       <c r="H12" s="27" t="inlineStr">
         <is>
-          <t>3 x 8/side</t>
+          <t>3 x 6</t>
         </is>
       </c>
       <c r="I12" s="28" t="n"/>
       <c r="J12" s="25" t="inlineStr">
         <is>
-          <t>3 x 10/side</t>
+          <t>3 x 6</t>
         </is>
       </c>
       <c r="K12" s="26" t="n"/>
       <c r="L12" s="27" t="inlineStr">
         <is>
-          <t>2 x 8/side</t>
+          <t>2 x 4</t>
         </is>
       </c>
       <c r="M12" s="28" t="n"/>
@@ -3115,45 +3115,45 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>Nordic hamstring curl</t>
+          <t>Half-kneeling cable lift</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>Slower lowering than in block 1. Less band help if you used one.</t>
+          <t>Cable low on the side of the down knee. Pull up and across, hips stay square.</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>slow lower</t>
+          <t>controlled</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
         <is>
-          <t>90 s</t>
+          <t>45 s</t>
         </is>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>3 x 5</t>
+          <t>3 x 8/side</t>
         </is>
       </c>
       <c r="G26" s="26" t="n"/>
       <c r="H26" s="27" t="inlineStr">
         <is>
-          <t>3 x 6</t>
+          <t>3 x 8/side</t>
         </is>
       </c>
       <c r="I26" s="28" t="n"/>
       <c r="J26" s="25" t="inlineStr">
         <is>
-          <t>3 x 6</t>
+          <t>3 x 10/side</t>
         </is>
       </c>
       <c r="K26" s="26" t="n"/>
       <c r="L26" s="27" t="inlineStr">
         <is>
-          <t>2 x 4</t>
+          <t>2 x 8/side</t>
         </is>
       </c>
       <c r="M26" s="28" t="n"/>
@@ -3320,7 +3320,7 @@
       <c r="K31" s="26" t="n"/>
       <c r="L31" s="27" t="inlineStr">
         <is>
-          <t>30 min Z2</t>
+          <t>30 min Z2: first 20 min at the week-1 test pace (heart rate benchmark)</t>
         </is>
       </c>
       <c r="M31" s="28" t="n"/>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="H20" s="38" t="inlineStr">
         <is>
-          <t>Average heart rate over 20 minutes at one fixed pace on a track or treadmill. Same pace in week 1 and week 8. Lower heart rate at the same pace means better aerobic fitness.</t>
+          <t>Week 1 and week 8, on the Tuesday run: average heart rate over the first 20 minutes at one fixed pace on a track or treadmill. Same pace both times. Lower heart rate at the same pace means better aerobic fitness.</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="H21" s="38" t="inlineStr">
         <is>
-          <t>Enter load x reps @ RIR (e.g. 100 x 5 @ 2). Week 1: best set of the week. Week 8: top set. The e1RM table below compares both on one scale.</t>
+          <t>Enter load x reps @ RIR (e.g. 100 x 5 @ 2). Week 1: the benchmark top set. Week 8: the test top set. The e1RM table below compares both on one scale.</t>
         </is>
       </c>
     </row>
@@ -3675,12 +3675,12 @@
     <row r="23" ht="30" customHeight="1">
       <c r="B23" s="37" t="inlineStr">
         <is>
-          <t>Trap bar deadlift</t>
+          <t>Chin-ups, max strict reps</t>
         </is>
       </c>
       <c r="H23" s="38" t="inlineStr">
         <is>
-          <t>Same as squat.</t>
+          <t>Bodyweight, full hang to chin over the bar, no swing. First chin-up set on Day A in week 1 and week 8.</t>
         </is>
       </c>
     </row>
@@ -3700,6 +3700,7 @@
     <row r="26" ht="22" customHeight="1">
       <c r="B26" s="10" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="B28" s="31" t="inlineStr">
         <is>
@@ -3817,30 +3818,18 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="42" t="inlineStr">
-        <is>
-          <t>Trap bar deadlift</t>
-        </is>
-      </c>
+      <c r="B33" s="42" t="n"/>
       <c r="C33" s="43" t="n"/>
       <c r="D33" s="43" t="n"/>
       <c r="E33" s="43" t="n"/>
-      <c r="F33" s="44">
-        <f>IF(C33="","",ROUND(C33*(1+(D33+E33)/30),1))</f>
-        <v/>
-      </c>
+      <c r="F33" s="44" t="n"/>
       <c r="G33" s="43" t="n"/>
       <c r="H33" s="43" t="n"/>
       <c r="I33" s="43" t="n"/>
-      <c r="J33" s="44">
-        <f>IF(G33="","",ROUND(G33*(1+(H33+I33)/30),1))</f>
-        <v/>
-      </c>
-      <c r="K33" s="45">
-        <f>IF(OR(F33="",J33=""),"",J33/F33-1)</f>
-        <v/>
-      </c>
-    </row>
+      <c r="J33" s="44" t="n"/>
+      <c r="K33" s="45" t="n"/>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="B35" s="46" t="inlineStr">
         <is>
